--- a/bug-tracker/UBA-bugs-tracker.xlsx
+++ b/bug-tracker/UBA-bugs-tracker.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\DEV\UBA6-release\bug-tracker\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\DEV\UBA6-maintenance\bug-tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E45D976-C5D9-4015-B05A-A7EFFB0DCC42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A117F1C-0413-415F-B52B-9E6AEA6165E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5B816FF3-3B79-4319-AB68-882518EDFCB6}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5B816FF3-3B79-4319-AB68-882518EDFCB6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="99">
   <si>
     <t>Num</t>
   </si>
@@ -368,12 +368,18 @@
   <si>
     <t>הגדרת סדר הטסטים לא נכונה - תוקן</t>
   </si>
+  <si>
+    <t>tryAgagin</t>
+  </si>
+  <si>
+    <t>18.08.2026</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -448,6 +454,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -504,7 +518,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -583,6 +597,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1395,10 +1412,12 @@
       <c r="F17" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G17" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H17" s="6"/>
+      <c r="G17" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>98</v>
+      </c>
       <c r="I17" s="21" t="s">
         <v>55</v>
       </c>
@@ -1425,10 +1444,12 @@
       <c r="F18" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G18" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H18" s="6"/>
+      <c r="G18" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>98</v>
+      </c>
       <c r="I18" s="21" t="s">
         <v>56</v>
       </c>
@@ -1517,10 +1538,12 @@
       <c r="F21" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G21" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H21" s="6"/>
+      <c r="G21" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>98</v>
+      </c>
       <c r="I21" s="21" t="s">
         <v>55</v>
       </c>
@@ -1547,10 +1570,12 @@
       <c r="F22" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G22" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H22" s="6"/>
+      <c r="G22" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>98</v>
+      </c>
       <c r="I22" s="20"/>
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
@@ -1575,10 +1600,12 @@
       <c r="F23" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G23" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H23" s="6"/>
+      <c r="G23" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>98</v>
+      </c>
       <c r="I23" s="20"/>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
@@ -1603,8 +1630,8 @@
       <c r="F24" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G24" s="10" t="s">
-        <v>18</v>
+      <c r="G24" s="9" t="s">
+        <v>11</v>
       </c>
       <c r="H24" s="6"/>
       <c r="I24" s="22"/>
@@ -1733,10 +1760,12 @@
       <c r="F28" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G28" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H28" s="6"/>
+      <c r="G28" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>98</v>
+      </c>
       <c r="I28" s="20"/>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>

--- a/bug-tracker/UBA-bugs-tracker.xlsx
+++ b/bug-tracker/UBA-bugs-tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\DEV\UBA6-maintenance\bug-tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A117F1C-0413-415F-B52B-9E6AEA6165E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5AAEBF9-E3C1-4863-A8FB-03DDA3A8C7A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5B816FF3-3B79-4319-AB68-882518EDFCB6}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="116">
   <si>
     <t>Num</t>
   </si>
@@ -298,7 +298,46 @@
     <t>להוריד את העמודה החדשה של UBA S/N - יש כפילות</t>
   </si>
   <si>
-    <t>database was overrided</t>
+    <t>open/closed</t>
+  </si>
+  <si>
+    <t>[2026-08-06 10:15:30.234] [error]: [a67e817e-12af-4e8a-864c-402318e87f52] ****Error: Command failed: "C:\Program Files\LibreOffice\program\soffice.exe" --headless --nologo --nofirststartwizard --convert-to pdf:calc_pdf_Export --outdir "C:\Users\amicell\uba6-work\UBA6-release\web-console\server\utils" "C:\Users\amicell\uba6-work\UBA6-release\web-console\server\utils\output-badf3ca5-4f4d-4075-91c4-469cb572d802.xlsx"     - sync   amicell-data\reports-data  folder (also bug #12)
+The system cannot find the path specified.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">NEW FEATURE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>in version (28/7)</t>
+    </r>
+  </si>
+  <si>
+    <t>09.08.2026</t>
+  </si>
+  <si>
+    <t>sync   amicell-data\reports-data  folder (also bug #3)</t>
+  </si>
+  <si>
+    <t>tryAgain</t>
+  </si>
+  <si>
+    <t>18.08.2026</t>
   </si>
   <si>
     <r>
@@ -324,62 +363,74 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">NEW FEATURE </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>in version (28/7)</t>
-    </r>
-  </si>
-  <si>
     <t>3.08.2026</t>
   </si>
   <si>
     <t>checked in ver Jul 30th</t>
   </si>
   <si>
-    <t>open/closed</t>
-  </si>
-  <si>
-    <t>sync   amicell-data\reports-data  folder (also bug #3)</t>
-  </si>
-  <si>
-    <t>[2026-08-06 10:15:30.234] [error]: [a67e817e-12af-4e8a-864c-402318e87f52] ****Error: Command failed: "C:\Program Files\LibreOffice\program\soffice.exe" --headless --nologo --nofirststartwizard --convert-to pdf:calc_pdf_Export --outdir "C:\Users\amicell\uba6-work\UBA6-release\web-console\server\utils" "C:\Users\amicell\uba6-work\UBA6-release\web-console\server\utils\output-badf3ca5-4f4d-4075-91c4-469cb572d802.xlsx"     - sync   amicell-data\reports-data  folder (also bug #12)
-The system cannot find the path specified.</t>
-  </si>
-  <si>
-    <t>09.08.2026</t>
+    <t>database was overrided</t>
   </si>
   <si>
     <t>הגדרת סדר הטסטים לא נכונה - תוקן</t>
   </si>
   <si>
-    <t>tryAgagin</t>
-  </si>
-  <si>
-    <t>18.08.2026</t>
+    <t>timer</t>
+  </si>
+  <si>
+    <t>ה timer מתאפס בהפעלה של יותר מ UBA אחד. הערה- בעיקר כשאר לוחצים PAUSE על אחד ה UBA</t>
+  </si>
+  <si>
+    <t>19.08.2026</t>
+  </si>
+  <si>
+    <t>PDF file</t>
+  </si>
+  <si>
+    <t>שם קובץ PDF - כולל SN+PN+fullDate</t>
+  </si>
+  <si>
+    <t>חזרה ל Step 1</t>
+  </si>
+  <si>
+    <t>בעצירת test תצוגת Step ה web חזרה ל Step 1 במקום Step 4. בעצירת אחד מהערוצים הנבדקים</t>
+  </si>
+  <si>
+    <t>DUAL - תצוגה שגויה</t>
+  </si>
+  <si>
+    <t>בסוף DUAL test התצוגה בצד СH B - הופיעה כ CH AB</t>
+  </si>
+  <si>
+    <t>PDF file format</t>
+  </si>
+  <si>
+    <t>להגדיל את ה font, מספור test מתחיל ב 0</t>
+  </si>
+  <si>
+    <t>לאחר סיום DUAL test תצוגה לא חזרה למקור - 2 צדדים</t>
+  </si>
+  <si>
+    <t>טעינה / פריקה לפי SOC</t>
+  </si>
+  <si>
+    <t>לא מתבצע תנאי טעינה/ פריקה לפי SOC .</t>
+  </si>
+  <si>
+    <t>24.08.2026</t>
+  </si>
+  <si>
+    <t>הוגדר ניסוי DUAL , כאשר לאחר משך הניסוי של 3+ שעות התקבלו תוצאות עבור שני ערוצים נפרדים עם תוצאות שונות הן מבחינת זמני הרצה, הן מבחינת תוצאות חשמליות.</t>
+  </si>
+  <si>
+    <t>האם יש לך נתונים נוספים של ה test?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -434,21 +485,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF7030A0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF7030A0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FF92D050"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -477,7 +513,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -505,20 +541,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -536,13 +563,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -560,46 +581,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -924,6 +937,7 @@
     <col min="3" max="3" width="72.88671875" customWidth="1"/>
     <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.88671875" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="36.44140625" customWidth="1"/>
     <col min="10" max="10" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -979,24 +993,24 @@
       <c r="C4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="19">
         <v>45116</v>
       </c>
-      <c r="E4" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="9" t="s">
+      <c r="E4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="20" t="s">
         <v>11</v>
       </c>
       <c r="H4" s="6"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="8" t="s">
+      <c r="I4" s="13"/>
+      <c r="J4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="7" t="s">
         <v>53</v>
       </c>
       <c r="L4" s="6"/>
@@ -1011,20 +1025,20 @@
       <c r="C5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="19">
         <v>45116</v>
       </c>
-      <c r="E5" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="9" t="s">
+      <c r="E5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="20" t="s">
         <v>11</v>
       </c>
       <c r="H5" s="6"/>
-      <c r="I5" s="20"/>
+      <c r="I5" s="13"/>
       <c r="J5" s="5" t="s">
         <v>72</v>
       </c>
@@ -1043,21 +1057,21 @@
       <c r="C6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="19">
         <v>45116</v>
       </c>
-      <c r="E6" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="28" t="s">
-        <v>92</v>
+      <c r="E6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>87</v>
       </c>
       <c r="H6" s="6"/>
-      <c r="I6" s="27" t="s">
-        <v>94</v>
+      <c r="I6" s="14" t="s">
+        <v>88</v>
       </c>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
@@ -1073,20 +1087,20 @@
       <c r="C7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="19">
         <v>45116</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="9" t="s">
+      <c r="E7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="20" t="s">
         <v>11</v>
       </c>
       <c r="H7" s="6"/>
-      <c r="I7" s="20"/>
+      <c r="I7" s="13"/>
       <c r="J7" s="5" t="s">
         <v>72</v>
       </c>
@@ -1105,24 +1119,24 @@
       <c r="C8" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="19">
         <v>45116</v>
       </c>
-      <c r="E8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="9" t="s">
+      <c r="E8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="20" t="s">
         <v>11</v>
       </c>
       <c r="H8" s="6"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="8" t="s">
+      <c r="I8" s="13"/>
+      <c r="J8" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K8" s="8" t="s">
+      <c r="K8" s="7" t="s">
         <v>53</v>
       </c>
       <c r="L8" s="6"/>
@@ -1137,20 +1151,20 @@
       <c r="C9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="19">
         <v>45116</v>
       </c>
-      <c r="E9" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="9" t="s">
+      <c r="E9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="20" t="s">
         <v>11</v>
       </c>
       <c r="H9" s="6"/>
-      <c r="I9" s="20"/>
+      <c r="I9" s="13"/>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
       <c r="L9" s="6"/>
@@ -1159,34 +1173,34 @@
       <c r="A10" s="5">
         <v>7</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="9" t="s">
         <v>24</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" s="8" t="s">
+      <c r="E10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="I10" s="21" t="s">
+      <c r="I10" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="J10" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="K10" s="8" t="s">
+      <c r="K10" s="7" t="s">
         <v>53</v>
       </c>
       <c r="L10" s="6"/>
@@ -1198,31 +1212,31 @@
       <c r="B11" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H11" s="8" t="s">
+      <c r="E11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="I11" s="21" t="s">
+      <c r="I11" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="J11" s="8" t="s">
+      <c r="J11" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="K11" s="8" t="s">
+      <c r="K11" s="7" t="s">
         <v>53</v>
       </c>
       <c r="L11" s="6"/>
@@ -1234,29 +1248,29 @@
       <c r="B12" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H12" s="8" t="s">
+      <c r="E12" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="I12" s="21" t="s">
+      <c r="I12" s="15" t="s">
         <v>54</v>
       </c>
       <c r="J12" s="5"/>
-      <c r="K12" s="12" t="s">
+      <c r="K12" s="10" t="s">
         <v>68</v>
       </c>
       <c r="L12" s="6"/>
@@ -1271,20 +1285,20 @@
       <c r="C13" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="9" t="s">
+      <c r="E13" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="20" t="s">
         <v>11</v>
       </c>
       <c r="H13" s="6"/>
-      <c r="I13" s="20"/>
+      <c r="I13" s="13"/>
       <c r="J13" s="5" t="s">
         <v>26</v>
       </c>
@@ -1297,37 +1311,37 @@
       <c r="A14" s="5">
         <v>11</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="11" t="s">
         <v>34</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="10" t="s">
+      <c r="E14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="I14" s="21" t="s">
+      <c r="I14" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="J14" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K14" s="12" t="s">
+      <c r="K14" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="L14" s="11" t="s">
+      <c r="L14" s="9" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1341,23 +1355,23 @@
       <c r="C15" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E15" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="H15" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="I15" s="20" t="s">
-        <v>93</v>
+      <c r="E15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="H15" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>91</v>
       </c>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
@@ -1370,23 +1384,23 @@
       <c r="B16" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E16" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" s="29" t="s">
+      <c r="E16" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="23" t="s">
         <v>11</v>
       </c>
       <c r="H16" s="6"/>
-      <c r="I16" s="20"/>
+      <c r="I16" s="13"/>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
       <c r="L16" s="6" t="s">
@@ -1400,25 +1414,25 @@
       <c r="B17" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E17" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="30" t="s">
-        <v>97</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="I17" s="21" t="s">
+      <c r="E17" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="I17" s="15" t="s">
         <v>55</v>
       </c>
       <c r="J17" s="5"/>
@@ -1435,22 +1449,22 @@
       <c r="C18" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E18" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" s="30" t="s">
-        <v>97</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="I18" s="21" t="s">
+      <c r="E18" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="I18" s="15" t="s">
         <v>56</v>
       </c>
       <c r="J18" s="5"/>
@@ -1464,24 +1478,24 @@
       <c r="B19" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E19" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19" s="18" t="s">
+      <c r="E19" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="21" t="s">
         <v>11</v>
       </c>
       <c r="H19" s="6"/>
-      <c r="I19" s="21" t="s">
-        <v>88</v>
+      <c r="I19" s="15" t="s">
+        <v>94</v>
       </c>
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
@@ -1497,25 +1511,25 @@
       <c r="C20" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E20" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20" s="18" t="s">
+      <c r="E20" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="21" t="s">
         <v>11</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="I20" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="J20" s="19"/>
+        <v>95</v>
+      </c>
+      <c r="I20" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="J20" s="17"/>
       <c r="K20" s="5"/>
       <c r="L20" s="6"/>
     </row>
@@ -1526,25 +1540,25 @@
       <c r="B21" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E21" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21" s="30" t="s">
-        <v>97</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="I21" s="21" t="s">
+      <c r="E21" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="I21" s="15" t="s">
         <v>55</v>
       </c>
       <c r="J21" s="5"/>
@@ -1558,25 +1572,25 @@
       <c r="B22" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="E22" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22" s="30" t="s">
-        <v>97</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="I22" s="20"/>
+      <c r="E22" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="I22" s="13"/>
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
       <c r="L22" s="6"/>
@@ -1588,25 +1602,25 @@
       <c r="B23" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="E23" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F23" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23" s="30" t="s">
-        <v>97</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="I23" s="20"/>
+      <c r="F23" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="I23" s="13"/>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
       <c r="L23" s="6"/>
@@ -1618,23 +1632,23 @@
       <c r="B24" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F24" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G24" s="9" t="s">
+      <c r="F24" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="20" t="s">
         <v>11</v>
       </c>
       <c r="H24" s="6"/>
-      <c r="I24" s="22"/>
+      <c r="I24" s="18"/>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
       <c r="L24" s="6"/>
@@ -1646,26 +1660,26 @@
       <c r="B25" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E25" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F25" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H25" s="8" t="s">
+      <c r="F25" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H25" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I25" s="20" t="s">
-        <v>87</v>
+      <c r="I25" s="13" t="s">
+        <v>97</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>26</v>
@@ -1682,26 +1696,26 @@
       <c r="B26" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F26" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H26" s="8" t="s">
+      <c r="F26" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I26" s="21" t="s">
-        <v>96</v>
+      <c r="I26" s="15" t="s">
+        <v>98</v>
       </c>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
@@ -1714,25 +1728,25 @@
       <c r="B27" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E27" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H27" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="I27" s="20"/>
+      <c r="E27" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H27" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="I27" s="13"/>
       <c r="J27" s="5" t="s">
         <v>26</v>
       </c>
@@ -1748,25 +1762,25 @@
       <c r="B28" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="E28" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G28" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="I28" s="20"/>
+      <c r="E28" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="I28" s="13"/>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
       <c r="L28" s="6"/>
@@ -1778,25 +1792,25 @@
       <c r="B29" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="D29" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="E29" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G29" s="9" t="s">
+      <c r="E29" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" s="20" t="s">
         <v>11</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="I29" s="20"/>
+        <v>90</v>
+      </c>
+      <c r="I29" s="13"/>
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
       <c r="L29" s="6"/>
@@ -1808,126 +1822,340 @@
       <c r="B30" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="D30" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="E30" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G30" s="9" t="s">
+      <c r="E30" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" s="20" t="s">
         <v>11</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="I30" s="20"/>
+        <v>90</v>
+      </c>
+      <c r="I30" s="13"/>
       <c r="J30" s="5"/>
       <c r="K30" s="5"/>
       <c r="L30" s="6"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="15">
+    <row r="31" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="5">
         <v>28</v>
       </c>
-      <c r="B31" s="16"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="24"/>
+      <c r="B31" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" s="20" t="s">
+        <v>11</v>
+      </c>
       <c r="H31" s="16"/>
-      <c r="I31" s="23"/>
-      <c r="J31" s="15"/>
-      <c r="K31" s="15"/>
-      <c r="L31" s="16"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="6"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C32" s="25"/>
-      <c r="I32" s="22"/>
-    </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C33" s="2"/>
-      <c r="I33" s="22"/>
-    </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C34" s="2"/>
-      <c r="I34" s="22"/>
-    </row>
-    <row r="35" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C35" s="2"/>
-      <c r="I35" s="22"/>
-    </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C36" s="2"/>
-      <c r="I36" s="22"/>
-    </row>
-    <row r="37" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C37" s="2"/>
-      <c r="I37" s="22"/>
-    </row>
-    <row r="38" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C38" s="2"/>
-      <c r="I38" s="22"/>
-    </row>
-    <row r="39" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C39" s="2"/>
-      <c r="I39" s="22"/>
-    </row>
-    <row r="40" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C40" s="2"/>
-      <c r="I40" s="22"/>
-    </row>
-    <row r="41" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C41" s="2"/>
-      <c r="I41" s="22"/>
-    </row>
-    <row r="42" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="5">
+        <v>29</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H32" s="7"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="6"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="5">
+        <v>30</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H33" s="6"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="6"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="5">
+        <v>31</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H34" s="6"/>
+      <c r="I34" s="13"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="6"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="5">
+        <v>32</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H35" s="16"/>
+      <c r="I35" s="13"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="6"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="5">
+        <v>33</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H36" s="7"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="6"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="5">
+        <v>34</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H37" s="16"/>
+      <c r="I37" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="6"/>
+    </row>
+    <row r="38" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="5">
+        <v>35</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H38" s="7"/>
+      <c r="I38" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="6"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" s="5"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="16"/>
+      <c r="I39" s="13"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="6"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" s="5"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="13"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="6"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" s="5"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="16"/>
+      <c r="I41" s="13"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="6"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C42" s="2"/>
-      <c r="I42" s="22"/>
-    </row>
-    <row r="43" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I42" s="18"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C43" s="2"/>
-      <c r="I43" s="22"/>
-    </row>
-    <row r="44" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I43" s="18"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C44" s="2"/>
-      <c r="I44" s="22"/>
-    </row>
-    <row r="45" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I44" s="18"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C45" s="2"/>
-      <c r="I45" s="22"/>
-    </row>
-    <row r="46" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I45" s="18"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C46" s="2"/>
-      <c r="I46" s="22"/>
-    </row>
-    <row r="47" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I46" s="18"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C47" s="2"/>
-      <c r="I47" s="22"/>
-    </row>
-    <row r="48" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="I48" s="22"/>
+      <c r="I47" s="18"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I48" s="18"/>
     </row>
     <row r="49" spans="9:9" x14ac:dyDescent="0.3">
-      <c r="I49" s="22"/>
+      <c r="I49" s="18"/>
     </row>
     <row r="50" spans="9:9" x14ac:dyDescent="0.3">
-      <c r="I50" s="22"/>
+      <c r="I50" s="18"/>
     </row>
     <row r="51" spans="9:9" x14ac:dyDescent="0.3">
-      <c r="I51" s="22"/>
+      <c r="I51" s="18"/>
     </row>
     <row r="52" spans="9:9" x14ac:dyDescent="0.3">
-      <c r="I52" s="22"/>
+      <c r="I52" s="18"/>
     </row>
     <row r="53" spans="9:9" x14ac:dyDescent="0.3">
-      <c r="I53" s="22"/>
+      <c r="I53" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/bug-tracker/UBA-bugs-tracker.xlsx
+++ b/bug-tracker/UBA-bugs-tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\DEV\UBA6-maintenance\bug-tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5AAEBF9-E3C1-4863-A8FB-03DDA3A8C7A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBAD710D-7C52-4D40-9A32-C903698B6B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5B816FF3-3B79-4319-AB68-882518EDFCB6}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="121">
   <si>
     <t>Num</t>
   </si>
@@ -424,6 +424,21 @@
   </si>
   <si>
     <t>האם יש לך נתונים נוספים של ה test?</t>
+  </si>
+  <si>
+    <t>test charge/discharge limit</t>
+  </si>
+  <si>
+    <t>לא עובד כ stop condition ל טסט - CHARGE?DISCHARGE limit</t>
+  </si>
+  <si>
+    <t>30.08.2026</t>
+  </si>
+  <si>
+    <t>display EWI message - התראות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">התראות והודעות על LCD screen ב UBA </t>
   </si>
 </sst>
 </file>
@@ -2074,13 +2089,27 @@
       <c r="L38" s="6"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" s="5"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="8"/>
+      <c r="A39" s="5">
+        <v>36</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G39" s="20" t="s">
+        <v>11</v>
+      </c>
       <c r="H39" s="16"/>
       <c r="I39" s="13"/>
       <c r="J39" s="5"/>
@@ -2088,13 +2117,27 @@
       <c r="L39" s="6"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" s="5"/>
-      <c r="B40" s="6"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="8"/>
+      <c r="A40" s="5">
+        <v>37</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G40" s="20" t="s">
+        <v>11</v>
+      </c>
       <c r="H40" s="7"/>
       <c r="I40" s="13"/>
       <c r="J40" s="5"/>

--- a/bug-tracker/UBA-bugs-tracker.xlsx
+++ b/bug-tracker/UBA-bugs-tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\DEV\UBA6-maintenance\bug-tracker\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\AnalysisResults\UBA-6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBAD710D-7C52-4D40-9A32-C903698B6B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA37E361-6390-438F-90CF-0CBB120A4EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5B816FF3-3B79-4319-AB68-882518EDFCB6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5B816FF3-3B79-4319-AB68-882518EDFCB6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="138">
   <si>
     <t>Num</t>
   </si>
@@ -439,6 +439,57 @@
   </si>
   <si>
     <t xml:space="preserve">התראות והודעות על LCD screen ב UBA </t>
+  </si>
+  <si>
+    <t>תקשורת- WEB/ UBA</t>
+  </si>
+  <si>
+    <t>בבדיקה ארוכה מעל שעה יש עיבוד תקשורת בין ה WEB ל UBA , המכשיר ממשיך לעבוד , תקלת תקשורת לא מדווחת בזמן אמת, ניתן לזהות רק לאחר עצירת ניסוי. בבדיקה נוכחו שני UBA , כאשר אחד מהם המשיך לפעול לאחר העצירה ייזומה, המאוור עבד אך צג לא הציג איזה שלב מתבצע. סכנה בטיחותית.</t>
+  </si>
+  <si>
+    <t>TIME</t>
+  </si>
+  <si>
+    <t>אין סנכרון של השעון בין WEB לUBA . בצורה ראנדומאלית , באותו המכשיר ערוץ אחד מציג זמן אמת תקין, בערוץ השני זמן כל שהוא שהוא ...</t>
+  </si>
+  <si>
+    <t>22.09.2026</t>
+  </si>
+  <si>
+    <t>7.09.2026</t>
+  </si>
+  <si>
+    <t>29.09.2026</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>לא מתקיים תאי של הגבלת זמן ל STEP</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t xml:space="preserve">זרם טעינה בפועל לא תואם את ההגדרה לפי תוכנית </t>
+  </si>
+  <si>
+    <t>Graph</t>
+  </si>
+  <si>
+    <t xml:space="preserve">סקלה של זרם מוצגת במיליאמפר כאשר  בפועל מתועדים ערכים של אמפרים </t>
+  </si>
+  <si>
+    <t>קצב דגימה מוגדר 1msec , כאשר בפועל הדגימה בוצעה לפי קצב לא תואם את הגדרה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ציון זמן הרצת STEP </t>
+  </si>
+  <si>
+    <t>כאשר התוכנית מרובת שלבים רצה וקורה עיבוד תקשורת , לא ניתן לזהות עיבוד תקשורת. הרצת זמן STEP על  המסך של ה UBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">תמונות מצורפות </t>
   </si>
 </sst>
 </file>
@@ -560,13 +611,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -592,9 +640,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -648,9 +693,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -688,7 +733,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -794,7 +839,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -936,7 +981,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -945,1260 +990,1465 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E8ABA1E-CC26-499E-82DE-E3065ED1E830}">
   <dimension ref="A3:L53"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="1"/>
-    <col min="2" max="2" width="42.5546875" customWidth="1"/>
-    <col min="3" max="3" width="72.88671875" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.88671875" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="2" max="2" width="42.5703125" customWidth="1"/>
+    <col min="3" max="3" width="72.85546875" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.85546875" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="36.44140625" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="34.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.42578125" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="34.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="5">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
         <v>1</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="17">
         <v>45116</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="7" t="s">
+      <c r="E4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="5"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="L4" s="6"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="5">
+      <c r="L4" s="5"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
         <v>2</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="17">
         <v>45116</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="5" t="s">
+      <c r="E5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="5"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="L5" s="6"/>
-    </row>
-    <row r="6" spans="1:12" ht="216" x14ac:dyDescent="0.3">
-      <c r="A6" s="5">
+      <c r="L5" s="5"/>
+    </row>
+    <row r="6" spans="1:12" ht="270" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
         <v>3</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="17">
         <v>45116</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="22" t="s">
+      <c r="E6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="H6" s="6"/>
-      <c r="I6" s="14" t="s">
+      <c r="H6" s="5"/>
+      <c r="I6" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="6"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="5">
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="5"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
         <v>4</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="17">
         <v>45116</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" s="6"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="5" t="s">
+      <c r="E7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K7" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="L7" s="6"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="5">
+      <c r="L7" s="5"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
         <v>5</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="17">
         <v>45116</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H8" s="6"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="7" t="s">
+      <c r="E8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="5"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="K8" s="7" t="s">
+      <c r="K8" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="L8" s="6"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="5">
+      <c r="L8" s="5"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
         <v>6</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="17">
         <v>45116</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H9" s="6"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="6"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="5">
+      <c r="E9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="5"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="5"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
         <v>7</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" s="7" t="s">
+      <c r="E10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="I10" s="15" t="s">
+      <c r="I10" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="J10" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="K10" s="7" t="s">
+      <c r="K10" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="L10" s="6"/>
-    </row>
-    <row r="11" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="5">
+      <c r="L10" s="5"/>
+    </row>
+    <row r="11" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
         <v>8</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H11" s="7" t="s">
+      <c r="E11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="I11" s="15" t="s">
+      <c r="I11" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="J11" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="K11" s="7" t="s">
+      <c r="K11" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="L11" s="6"/>
-    </row>
-    <row r="12" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="5">
-        <v>9</v>
-      </c>
-      <c r="B12" s="6" t="s">
+      <c r="L11" s="5"/>
+    </row>
+    <row r="12" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>9</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H12" s="7" t="s">
+      <c r="E12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="I12" s="15" t="s">
+      <c r="I12" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="J12" s="5"/>
-      <c r="K12" s="10" t="s">
+      <c r="J12" s="4"/>
+      <c r="K12" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="L12" s="6"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="5">
-        <v>10</v>
-      </c>
-      <c r="B13" s="6" t="s">
+      <c r="L12" s="5"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>10</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H13" s="6"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="5" t="s">
+      <c r="E13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="5"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="K13" s="5" t="s">
+      <c r="K13" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="L13" s="6"/>
-    </row>
-    <row r="14" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="5">
-        <v>11</v>
-      </c>
-      <c r="B14" s="11" t="s">
+      <c r="L13" s="5"/>
+    </row>
+    <row r="14" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>11</v>
+      </c>
+      <c r="B14" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="8" t="s">
+      <c r="E14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="H14" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="I14" s="15" t="s">
+      <c r="I14" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="J14" s="7" t="s">
+      <c r="J14" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="K14" s="10" t="s">
+      <c r="K14" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="L14" s="9" t="s">
+      <c r="L14" s="8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="5">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
         <v>12</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" s="23" t="s">
+      <c r="E15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="16" t="s">
+      <c r="H15" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="I15" s="13" t="s">
+      <c r="I15" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="6"/>
-    </row>
-    <row r="16" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="5">
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="5"/>
+    </row>
+    <row r="16" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
         <v>13</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="H16" s="6"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="6" t="s">
+      <c r="E16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16" s="5"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="5">
+    <row r="17" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
         <v>14</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E17" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="24" t="s">
+      <c r="E17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="H17" s="7" t="s">
+      <c r="H17" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="I17" s="15" t="s">
+      <c r="I17" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="6"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="5">
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="5"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
         <v>15</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E18" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" s="24" t="s">
+      <c r="E18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="H18" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="I18" s="15" t="s">
+      <c r="I18" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="6"/>
-    </row>
-    <row r="19" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="5">
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="5"/>
+    </row>
+    <row r="19" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
         <v>16</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E19" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="H19" s="6"/>
-      <c r="I19" s="15" t="s">
+      <c r="E19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H19" s="5"/>
+      <c r="I19" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="6"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="5">
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="5"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
         <v>17</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E20" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="H20" s="3" t="s">
+      <c r="E20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="I20" s="17" t="s">
+      <c r="I20" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="J20" s="17"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="6"/>
-    </row>
-    <row r="21" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="5">
+      <c r="J20" s="15"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
         <v>18</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E21" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21" s="24" t="s">
+      <c r="E21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="H21" s="7" t="s">
+      <c r="H21" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="I21" s="15" t="s">
+      <c r="I21" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="6"/>
-    </row>
-    <row r="22" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="5">
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="5"/>
+    </row>
+    <row r="22" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
         <v>19</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E22" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22" s="24" t="s">
+      <c r="E22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="H22" s="7" t="s">
+      <c r="H22" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="I22" s="13"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
-      <c r="L22" s="6"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="5">
+      <c r="I22" s="11"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="5"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="4">
         <v>20</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="F23" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23" s="24" t="s">
+      <c r="F23" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="H23" s="7" t="s">
+      <c r="H23" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="I23" s="13"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5"/>
-      <c r="L23" s="6"/>
-    </row>
-    <row r="24" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="5">
+      <c r="I23" s="11"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="5"/>
+    </row>
+    <row r="24" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
         <v>21</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="F24" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G24" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H24" s="6"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
-      <c r="L24" s="6"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="5">
+      <c r="F24" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H24" s="5"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="5"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
         <v>22</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="F25" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G25" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H25" s="7" t="s">
+      <c r="F25" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H25" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="I25" s="13" t="s">
+      <c r="I25" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="J25" s="5" t="s">
+      <c r="J25" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="K25" s="5" t="s">
+      <c r="K25" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="L25" s="6"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="5">
+      <c r="L25" s="5"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
         <v>23</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="F26" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G26" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H26" s="7" t="s">
+      <c r="F26" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="I26" s="15" t="s">
+      <c r="I26" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
-      <c r="L26" s="6"/>
-    </row>
-    <row r="27" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="5">
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="5"/>
+    </row>
+    <row r="27" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="4">
         <v>24</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="E27" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G27" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H27" s="16" t="s">
+      <c r="E27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H27" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="I27" s="13"/>
-      <c r="J27" s="5" t="s">
+      <c r="I27" s="11"/>
+      <c r="J27" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="K27" s="5" t="s">
+      <c r="K27" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="L27" s="6"/>
-    </row>
-    <row r="28" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="5">
+      <c r="L27" s="5"/>
+    </row>
+    <row r="28" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="4">
         <v>25</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="E28" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G28" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H28" s="7" t="s">
+      <c r="E28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="I28" s="13"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="6"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="5">
+      <c r="I28" s="11"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="5"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="4">
         <v>26</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="E29" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G29" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H29" s="6" t="s">
+      <c r="E29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H29" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="I29" s="13"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
-      <c r="L29" s="6"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="5">
+      <c r="I29" s="11"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="5"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="4">
         <v>27</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C30" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="E30" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G30" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H30" s="6" t="s">
+      <c r="E30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H30" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="I30" s="13"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
-      <c r="L30" s="6"/>
-    </row>
-    <row r="31" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="5">
+      <c r="I30" s="11"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="5"/>
+    </row>
+    <row r="31" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="4">
         <v>28</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E31" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G31" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H31" s="16"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="5"/>
-      <c r="K31" s="5"/>
-      <c r="L31" s="6"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="5">
+      <c r="E31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="I31" s="11"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="5"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="4">
         <v>29</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="C32" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E32" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G32" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H32" s="7"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="5"/>
-      <c r="K32" s="5"/>
-      <c r="L32" s="6"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="5">
+      <c r="E32" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="I32" s="11"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="5"/>
+    </row>
+    <row r="33" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="4">
         <v>30</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E33" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G33" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H33" s="6"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="5"/>
-      <c r="K33" s="5"/>
-      <c r="L33" s="6"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="5">
+      <c r="E33" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="I33" s="11"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="5"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="4">
         <v>31</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C34" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E34" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G34" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H34" s="6"/>
-      <c r="I34" s="13"/>
-      <c r="J34" s="5"/>
-      <c r="K34" s="5"/>
-      <c r="L34" s="6"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="5">
+      <c r="E34" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="I34" s="11"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="5"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="4">
         <v>32</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C35" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D35" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E35" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G35" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H35" s="16"/>
-      <c r="I35" s="13"/>
-      <c r="J35" s="5"/>
-      <c r="K35" s="5"/>
-      <c r="L35" s="6"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="5">
+      <c r="E35" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="I35" s="11"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="5"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" s="4">
         <v>33</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="C36" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="D36" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E36" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G36" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H36" s="7"/>
-      <c r="I36" s="13"/>
-      <c r="J36" s="5"/>
-      <c r="K36" s="5"/>
-      <c r="L36" s="6"/>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A37" s="5">
+      <c r="E36" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="I36" s="11"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="4"/>
+      <c r="L36" s="5"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" s="4">
         <v>34</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="C37" s="9" t="s">
+      <c r="C37" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="D37" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="E37" s="7" t="s">
+      <c r="E37" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="F37" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G37" s="8" t="s">
+      <c r="F37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="H37" s="16"/>
-      <c r="I37" s="13" t="s">
+      <c r="H37" s="14"/>
+      <c r="I37" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
-      <c r="L37" s="6"/>
-    </row>
-    <row r="38" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A38" s="5">
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="5"/>
+    </row>
+    <row r="38" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A38" s="4">
         <v>35</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C38" s="9" t="s">
+      <c r="C38" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="D38" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="E38" s="7" t="s">
+      <c r="E38" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="F38" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G38" s="8" t="s">
+      <c r="F38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="H38" s="7"/>
-      <c r="I38" s="13" t="s">
+      <c r="H38" s="6"/>
+      <c r="I38" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="6"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" s="5">
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="5"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" s="4">
         <v>36</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="C39" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="D39" s="7" t="s">
+      <c r="D39" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="E39" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G39" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H39" s="16"/>
-      <c r="I39" s="13"/>
-      <c r="J39" s="5"/>
-      <c r="K39" s="5"/>
-      <c r="L39" s="6"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" s="5">
+      <c r="E39" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G39" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="I39" s="11"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
+      <c r="L39" s="5"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" s="4">
         <v>37</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C40" s="9" t="s">
+      <c r="C40" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="D40" s="7" t="s">
+      <c r="D40" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="E40" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G40" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H40" s="7"/>
-      <c r="I40" s="13"/>
-      <c r="J40" s="5"/>
-      <c r="K40" s="5"/>
-      <c r="L40" s="6"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" s="5"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="8"/>
-      <c r="H41" s="16"/>
-      <c r="I41" s="13"/>
-      <c r="J41" s="5"/>
-      <c r="K41" s="5"/>
-      <c r="L41" s="6"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C42" s="2"/>
-      <c r="I42" s="18"/>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C43" s="2"/>
-      <c r="I43" s="18"/>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C44" s="2"/>
-      <c r="I44" s="18"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C45" s="2"/>
-      <c r="I45" s="18"/>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C46" s="2"/>
-      <c r="I46" s="18"/>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C47" s="2"/>
-      <c r="I47" s="18"/>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="I48" s="18"/>
-    </row>
-    <row r="49" spans="9:9" x14ac:dyDescent="0.3">
-      <c r="I49" s="18"/>
-    </row>
-    <row r="50" spans="9:9" x14ac:dyDescent="0.3">
-      <c r="I50" s="18"/>
-    </row>
-    <row r="51" spans="9:9" x14ac:dyDescent="0.3">
-      <c r="I51" s="18"/>
-    </row>
-    <row r="52" spans="9:9" x14ac:dyDescent="0.3">
-      <c r="I52" s="18"/>
-    </row>
-    <row r="53" spans="9:9" x14ac:dyDescent="0.3">
-      <c r="I53" s="18"/>
+      <c r="E40" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G40" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="I40" s="11"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="5"/>
+    </row>
+    <row r="41" spans="1:12" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="4">
+        <v>38</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G41" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="I41" s="11"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="4">
+        <v>39</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G42" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H42" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="I42" s="11"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="5"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43" s="4">
+        <v>40</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F43" s="6"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
+      <c r="L43" s="5"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44" s="4">
+        <v>41</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F44" s="6"/>
+      <c r="G44" s="18"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" s="4">
+        <v>42</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F45" s="6"/>
+      <c r="G45" s="18"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="J45" s="4"/>
+      <c r="K45" s="4"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46" s="4">
+        <v>43</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F46" s="6"/>
+      <c r="G46" s="18"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A47" s="4">
+        <v>44</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F47" s="6"/>
+      <c r="G47" s="18"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48" s="4">
+        <v>45</v>
+      </c>
+      <c r="B48" s="5"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="18"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="11"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" s="4">
+        <v>46</v>
+      </c>
+      <c r="B49" s="5"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="18"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="11"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="4"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="18"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="11"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="I51" s="16"/>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="I52" s="16"/>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="I53" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
